--- a/data/trans_dic/P1803_2016_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P1803_2016_2023-Estudios-trans_dic.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,59%</t>
         </is>
       </c>
     </row>
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,64; 5,53</t>
+          <t>2,48; 5,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,83; 6,03</t>
+          <t>2,63; 5,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,02; 5,8</t>
+          <t>2,96; 5,63</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,61; 8,22</t>
+          <t>5,6; 8,1</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,07; 5,02</t>
+          <t>3,08; 5,03</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,74; 6,82</t>
+          <t>4,66; 6,62</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>8,54%</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,45; 5,32</t>
+          <t>3,37; 5,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,71; 45,55</t>
+          <t>6,53; 9,04</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,32; 6,43</t>
+          <t>4,3; 6,34</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,22; 9,89</t>
+          <t>8,48; 10,65</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,12; 5,43</t>
+          <t>4,13; 5,54</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,89; 30,14</t>
+          <t>7,59; 9,38</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>13,63%</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,79; 9,57</t>
+          <t>4,66; 9,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,29; 16,16</t>
+          <t>9,74; 15,3</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,5; 11,68</t>
+          <t>6,61; 11,47</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13,53; 18,76</t>
+          <t>12,83; 17,58</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,35; 9,85</t>
+          <t>6,29; 9,66</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,51; 16,48</t>
+          <t>11,75; 15,5</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>8,99%</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,86; 5,36</t>
+          <t>3,91; 5,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,02; 33,84</t>
+          <t>7,01; 9,02</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,71; 6,29</t>
+          <t>4,8; 6,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,73; 10,58</t>
+          <t>9,07; 10,79</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,52; 5,62</t>
+          <t>4,54; 5,61</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,7; 23,32</t>
+          <t>8,32; 9,64</t>
         </is>
       </c>
     </row>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>21770</t>
+          <t>23348</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>51081</t>
+          <t>54874</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>72851</t>
+          <t>78221</t>
         </is>
       </c>
     </row>
@@ -1101,32 +1101,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>19932; 41735</t>
+          <t>18727; 40010</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>14556; 31028</t>
+          <t>15189; 33569</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>30086; 57692</t>
+          <t>29403; 55982</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>42369; 62042</t>
+          <t>45982; 66530</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>53643; 87791</t>
+          <t>53892; 88044</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>60188; 86582</t>
+          <t>65229; 92710</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>410051</t>
+          <t>171653</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>188755</t>
+          <t>204416</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>598807</t>
+          <t>376068</t>
         </is>
       </c>
     </row>
@@ -1219,32 +1219,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>71694; 110409</t>
+          <t>70035; 108586</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>176676; 1043281</t>
+          <t>145604; 201670</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>85818; 127799</t>
+          <t>85528; 126006</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>139217; 221212</t>
+          <t>184020; 231119</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>167439; 220615</t>
+          <t>167760; 225133</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>357388; 1364430</t>
+          <t>334117; 412762</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>82686</t>
+          <t>86996</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>104830</t>
+          <t>110126</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>187515</t>
+          <t>197121</t>
         </is>
       </c>
     </row>
@@ -1337,32 +1337,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>26187; 52350</t>
+          <t>25478; 51201</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>66520; 104473</t>
+          <t>69286; 108886</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>35704; 64123</t>
+          <t>36288; 62998</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>89356; 123892</t>
+          <t>94309; 129168</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>69547; 107906</t>
+          <t>68920; 105844</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>163572; 215352</t>
+          <t>169985; 224131</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>514507</t>
+          <t>281996</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>344666</t>
+          <t>369415</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>859173</t>
+          <t>651411</t>
         </is>
       </c>
     </row>
@@ -1455,32 +1455,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>130268; 181117</t>
+          <t>132142; 182616</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>276909; 1168231</t>
+          <t>246681; 317741</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>166206; 222342</t>
+          <t>169654; 224336</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>282260; 386596</t>
+          <t>337907; 402070</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>312490; 388320</t>
+          <t>313388; 387783</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>617953; 1656994</t>
+          <t>602992; 698679</t>
         </is>
       </c>
     </row>
